--- a/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
+++ b/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
@@ -540,10 +540,10 @@
         <v>5534320</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11.4</v>
+        <v>3.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0352</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>5818340</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11.2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="6">
@@ -584,10 +584,10 @@
         <v>6092570</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11</v>
+        <v>2.9</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="7">
@@ -606,10 +606,10 @@
         <v>5914150</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11.6</v>
+        <v>3.3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0346</v>
+        <v>0.1217</v>
       </c>
     </row>
     <row r="8">
@@ -628,10 +628,10 @@
         <v>6328080</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>11.3</v>
+        <v>3.2</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>5619790</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="10">
@@ -672,10 +672,10 @@
         <v>35307250</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>11.3</v>
+        <v>3.1</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.1295</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
+++ b/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5036734320</v>
+        <v>15239095668</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5031200000</v>
+        <v>15222351098</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5534320</v>
+        <v>16744570</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1295</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5295218340</v>
+        <v>14897256470</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5289400000</v>
+        <v>14880887509</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5818340</v>
+        <v>16368961</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1338</v>
+        <v>0.1317</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5544792570</v>
+        <v>15029546598</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5538700000</v>
+        <v>15013032278</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6092570</v>
+        <v>16514320</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1384</v>
+        <v>0.1296</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5382414150</v>
+        <v>14743064031</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5376500000</v>
+        <v>14726864496</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5914150</v>
+        <v>16199535</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1217</v>
+        <v>0.1267</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5759128080</v>
+        <v>15430707999</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5752800000</v>
+        <v>15413752886</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6328080</v>
+        <v>16955113</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5114519790</v>
+        <v>13206720191</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5108900000</v>
+        <v>13192208775</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5619790</v>
+        <v>14511416</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1295</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>32132807250</v>
+        <v>88546390957</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>32097500000</v>
+        <v>88449097042</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>35307250</v>
+        <v>97293915</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>3.1</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.1295</v>
+        <v>0.1296</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
+++ b/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>15239095668</v>
+        <v>15239114108</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>15222351098</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>16744570</v>
+        <v>16763010</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.127</v>
+        <v>0.1271</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14897256470</v>
+        <v>14897274494</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>14880887509</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16368961</v>
+        <v>16386985</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>15029546598</v>
+        <v>15029564784</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>15013032278</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16514320</v>
+        <v>16532506</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1296</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14743064031</v>
+        <v>14743081870</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>14726864496</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16199535</v>
+        <v>16217374</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1267</v>
+        <v>0.1268</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15430707999</v>
+        <v>15430726669</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>15413752886</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16955113</v>
+        <v>16973783</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.131</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>13206720191</v>
+        <v>13206736170</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>13192208775</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>14511416</v>
+        <v>14527395</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1318</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>88546390957</v>
+        <v>88546498095</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>88449097042</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>97293915</v>
+        <v>97401053</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>3.1</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.1296</v>
+        <v>0.1297</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
+++ b/assets/xlsx/월별투자수익_2026-03-01_2026-08-31.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -103,11 +101,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -531,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>15239114108</v>
+        <v>902176124</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>15222351098</v>
+        <v>901681409</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>16763010</v>
+        <v>494715</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14897274494</v>
+        <v>867039710</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14880887509</v>
+        <v>866548525</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16386985</v>
+        <v>491185</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1318</v>
+        <v>0.0759</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>15029564784</v>
+        <v>900975563</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15013032278</v>
+        <v>900485952</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16532506</v>
+        <v>489611</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1298</v>
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14743081870</v>
+        <v>873940919</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14726864496</v>
+        <v>873465485</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>16217374</v>
+        <v>475434</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1268</v>
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15430726669</v>
+        <v>897858596</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>15413752886</v>
+        <v>897352825</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16973783</v>
+        <v>505771</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1311</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>13206736170</v>
+        <v>781086860</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>13192208775</v>
+        <v>780652554</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>14527395</v>
+        <v>434306</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.132</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>88546498095</v>
+        <v>5223077772</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>88449097042</v>
+        <v>5220186750</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>97401053</v>
+        <v>2891022</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.1297</v>
+        <v>0.0736</v>
       </c>
     </row>
   </sheetData>
